--- a/fund_data/trade_history.xlsx
+++ b/fund_data/trade_history.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/fund_data/trade_history.xlsx
+++ b/fund_data/trade_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,117 +478,78 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>赎回货币</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>513530</t>
+          <t>511880</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>华泰柏瑞港股通红利ETF</t>
+          <t>银华日利货币ETF</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.6075</v>
+        <v>100.2844</v>
       </c>
       <c r="F2" t="n">
-        <v>6220.839813374806</v>
+        <v>99.73589933855152</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0474600910961962</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>10000</v>
+        <v>10001.95482362704</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>偏离度-4.75% &lt; -3.0%（最低）</t>
+          <t>赎回货币基金用于买入红利</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>换仓卖</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>513530</t>
+          <t>563020</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>华泰柏瑞港股通红利ETF</t>
+          <t>易方达中证红利低波动ETF(场内)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6735</v>
+        <v>1.1645</v>
       </c>
       <c r="F3" t="n">
-        <v>6220.839813374806</v>
+        <v>8589.055237120683</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.002440994399721008</v>
+        <v>-0.03486343462639807</v>
       </c>
       <c r="H3" t="n">
-        <v>10410.57542768274</v>
+        <v>10001.95482362704</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>563020偏离度更低，差3.44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>换仓买</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>563020</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>易方达红利低波 ETF</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1.1717</v>
-      </c>
-      <c r="F4" t="n">
-        <v>8885.017860956506</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.0368573123466448</v>
-      </c>
-      <c r="H4" t="n">
-        <v>10410.57542768274</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>偏离度最低-3.69%</t>
+          <t>偏离度-3.49% &lt; -3.0%</t>
         </is>
       </c>
     </row>

--- a/fund_data/trade_history.xlsx
+++ b/fund_data/trade_history.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>action</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>shares</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>deviation</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
@@ -500,13 +488,13 @@
         <v>100.2844</v>
       </c>
       <c r="F2" t="n">
-        <v>99.73589933855152</v>
+        <v>9.973589933855152</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>10001.95482362704</v>
+        <v>1000.195482362704</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -539,13 +527,13 @@
         <v>1.1645</v>
       </c>
       <c r="F3" t="n">
-        <v>8589.055237120683</v>
+        <v>858.9055237120683</v>
       </c>
       <c r="G3" t="n">
         <v>-0.03486343462639807</v>
       </c>
       <c r="H3" t="n">
-        <v>10001.95482362704</v>
+        <v>1000.195482362704</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
